--- a/光伏配储项目/电价数据/2026/马坝站.xlsx
+++ b/光伏配储项目/电价数据/2026/马坝站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5124099999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7375700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5660599999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58428</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51402</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49547</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42705</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.25665</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42338</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32627</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03796</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04028</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.04219</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03384</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04647999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02415</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.02631</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02542</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.04902</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.02002</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01636</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04436</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03804</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.00852</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.68001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39562</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.57031</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039099999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7985099999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63049</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7387899999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.92722</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6597000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5834199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72084</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47346</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6239</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60356</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69165</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.00454</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6379400000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.5531699999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66744</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49381</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51746</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50491</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.55225</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42808</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26343</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.23873</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18902</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.1098</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19559</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23511</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01516</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03995</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.01002</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.12705</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.18984</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.02549</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04187</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03642</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.5737000000000001</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.47969</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49303</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58826</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53185</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67141</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.63317</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7191799999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7652899999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.4671</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44408</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50976</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44494</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44515</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25089</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20833</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23123</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.46443</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50003</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5251699999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6084400000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5760599999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59649</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46339</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48176</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40234</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44693</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47511</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12576</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19698</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56049</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40099</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.20949</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22172</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16621</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.11071</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02905</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.02948</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.00795</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23181</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02713</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10118</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19568</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10288</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10119</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16478</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44758</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41568</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3155</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.20878</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.21796</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.20955</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20389</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21098</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02866</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.17487</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09182999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0396</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03861</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04154</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04257</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04670000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04063</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03827000000000001</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05802</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03386</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46718</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.3508</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65362</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42244</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00878</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20387</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.03533</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33531</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91408</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86249</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88712</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6315299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18671</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86846</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53632</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33046</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03265</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5304</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7906599999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5297200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77264</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77728</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8736900000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49284</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39949</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20659</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62146</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5855399999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42713</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59562</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60129</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69041</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58028</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.22198</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8584299999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.7744500000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.77476</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.22862</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.53865</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26688</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35331</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91808</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46458</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4992200000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16607</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19291</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.01084</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44311</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59534</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88976</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44927</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16087</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6998799999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79072</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66453</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5793200000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50101</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4402</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43749</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41314</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49463</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55003</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15378</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27515</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56989</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8481300000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46439</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32337</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42169</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2791</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22522</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14128</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15266</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.04241</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14127</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13599</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1365</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.15499</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10766</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10727</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12567</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14045</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45149</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44372</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34823</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53722</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.13879</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.12069</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20032</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.15364</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24324</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.04101</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28646</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25979</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3599</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43519</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46503</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.51298</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.20438</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.46211</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6897799999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50973</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22188</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31384</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.11922</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.17979</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.12096</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.16983</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.20514</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.20505</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.20708</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34951</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34916</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36885</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>-0.01427</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>-0.01443</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>-0.01401</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>-0.00903</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>-0.01507</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>-0.01401</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>-0.01274</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>-0.01384</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>-0.01283</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.1689</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41769</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77018</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34425</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14847</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>-0.01554</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>-0.01846</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>-0.01789</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>-0.01894</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43268</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64112</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5985900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60656</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.4869</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81312</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48772</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8141499999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41858</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35987</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52703</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47958</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48246</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4075299999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>-0.0067</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.03354</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.02333</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>-0.008039999999999999</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>-0.008150000000000001</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.00298</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.14719</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.18421</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>-0.00547</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.20138</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.19899</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.20294</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43814</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50276</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6917300000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7129500000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.54622</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80645</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5824600000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5250199999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77006</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6721200000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4717</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48178</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46899</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5512899999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4412</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45407</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37921</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.21746</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.2599</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.20444</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>-0.01393</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.00497</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19679</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>-0.00529</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04746</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-0.04119</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.00851</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.00974</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.02195</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>-0.01039</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.21523</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.21527</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.21907</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36523</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44395</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25205</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22588</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22978</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.21443</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24913</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13967</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.24815</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.21196</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.20788</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.02123</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0431</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.21644</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16921</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18738</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23379</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.23054</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.19487</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.03817</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.17913</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.18799</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.15805</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.19408</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.20293</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.15203</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.19618</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.19863</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33762</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13532</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22417</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.21403</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.006990000000000001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30401</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.25735</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6263200000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.75903</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75093</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57502</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23208</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.19906</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19857</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.02477</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.01453</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.03921</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.2071</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20747</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.17892</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19098</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18611</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15887</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.21456</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.26427</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32154</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.14303</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.53144</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.19918</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.22719</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.12715</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.00341</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.00861</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>-0.004589999999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>-0.00182</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.21558</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14177</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.18115</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.21521</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.21862</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.20677</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.42135</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34062</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.84188</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54484</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.22168</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.20907</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.21893</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.21074</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.17666</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.26215</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.17666</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>-0.01576</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>-0.00036</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>-0.00019</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.21486</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>-0.00967</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.00169</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.16707</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.16506</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.17678</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>-0.00636</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.00148</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.00186</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>-0.00817</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.15381</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.00425</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.17671</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.23081</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.44192</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27564</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.32422</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3141600000000001</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.16302</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.26956</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>-0.00138</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.27793</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.21809</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.15978</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.19581</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.19167</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.22276</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21153</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.20975</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>-0.008710000000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.16631</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.00128</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.00349</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.18424</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.22084</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>-0.007940000000000001</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>-0.00201</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.0009699999999999999</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>-0.00317</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.17964</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.21563</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.00966</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.18131</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.01324</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.20916</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.42551</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.33158</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.21544</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.20044</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.25547</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="T141" t="n">
+        <v>-0.00767</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.20454</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.20309</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.21343</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.21496</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.21371</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.20806</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.21728</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>-0.01187</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.00195</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.21022</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.18341</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.009640000000000001</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.00189</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21203</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.0189</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.19194</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.00882</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.00435</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.02295</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01847</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01211</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.02489</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08728</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.00679</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>-0.009990000000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.00584</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.01191</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.21883</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.01533</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.18363</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.16491</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.20857</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.19939</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.14532</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.19536</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.20545</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.20117</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.20325</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.21482</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.20843</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.20555</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>-0.00031</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.00414</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.22419</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.18661</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19861</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.04559000000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.00345</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.00331</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.20619</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02264</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.23017</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.21823</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.22477</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39034</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.50227</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.20131</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32289</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>-0.01545</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.20329</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.16428</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.20454</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>-0.01883</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18467</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.03222</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20688</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.20444</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.20603</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.03732</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.03832</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>-0.04751</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21315</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.21385</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17568</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.1905</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.21034</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20716</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.20368</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37695</v>
       </c>
     </row>
   </sheetData>
